--- a/model/data/invoice/sale-invoices-from-digikala/1405-07-02-sale-zibavash-express.xlsx
+++ b/model/data/invoice/sale-invoices-from-digikala/1405-07-02-sale-zibavash-express.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="89">
   <si>
     <t>شیوه ارسال مرسوله</t>
   </si>
@@ -103,60 +103,12 @@
     <t>2ساعت</t>
   </si>
   <si>
-    <t>خط چشم</t>
-  </si>
-  <si>
-    <t>ریمل</t>
-  </si>
-  <si>
-    <t>ریمل گلدن رز مدل Flash رنگ زرشکی تیره شماره 10 | گارانتی اصالت و سلامت فیزیکی کالا</t>
-  </si>
-  <si>
     <t>1405/07/02</t>
   </si>
   <si>
-    <t>1405/07/04</t>
-  </si>
-  <si>
-    <t>قزوین-تاکستان</t>
-  </si>
-  <si>
-    <t>سفارش جدید</t>
-  </si>
-  <si>
     <t>مداد لب</t>
   </si>
   <si>
-    <t>مداد لب گلدن رز مدل DREAM شماره 510 | گارانتی اصالت و سلامت فیزیکی کالا</t>
-  </si>
-  <si>
-    <t>همدان-سرکان</t>
-  </si>
-  <si>
-    <t>مداد لب فلورمار مدل ضد آب شماره 205 | گارانتی اصالت و سلامت فیزیکی کالا</t>
-  </si>
-  <si>
-    <t>فارس-نورآباد</t>
-  </si>
-  <si>
-    <t>مداد لب فلورمار مدل بادوام شماره 201 | گارانتی اصالت و سلامت فیزیکی کالا</t>
-  </si>
-  <si>
-    <t>اردبیل-اردبیل</t>
-  </si>
-  <si>
-    <t>در انتظار جمع آوری</t>
-  </si>
-  <si>
-    <t>پریوش نورافکن</t>
-  </si>
-  <si>
-    <t>اردبیل،یعقوبیه، بل قاسم سلیمانی، بعد از خ. شاهد، خ. حجتی 1, پلاک ۱۳, واحد ۵</t>
-  </si>
-  <si>
-    <t>09148636580</t>
-  </si>
-  <si>
     <t>فیکساتور آرایش</t>
   </si>
   <si>
@@ -166,31 +118,169 @@
     <t>4ساعت</t>
   </si>
   <si>
-    <t>مازندران-تنکابن</t>
-  </si>
-  <si>
-    <t>مهسا سیاح مفضلی</t>
-  </si>
-  <si>
-    <t>بل فردوسی شرقی، ک. پسکلایه کوچک،ساختمان ارتین طبقه سوم, پلاک ۱, واحد ۶</t>
-  </si>
-  <si>
-    <t>09013605381</t>
-  </si>
-  <si>
-    <t>خط چشم آدور کوین مدل  3DMAX | گارانتی اصالت و سلامت فیزیکی کالا</t>
-  </si>
-  <si>
-    <t>خوزستان-اندیمشک</t>
-  </si>
-  <si>
-    <t>بیتا بیطارزاده</t>
-  </si>
-  <si>
-    <t>کوی نیرو، ب دزفول اندیمشک، ک. والفجر10، ک. نصر2, پلاک ۱۴, واحد ۸</t>
-  </si>
-  <si>
-    <t>09396172556</t>
+    <t>رژ لب مایع و لیپ گلاس</t>
+  </si>
+  <si>
+    <t>رژ لب مایع گلدن رز شماره 16 | گارانتی اصالت و سلامت فیزیکی کالا</t>
+  </si>
+  <si>
+    <t>1405/07/01</t>
+  </si>
+  <si>
+    <t>یزد-یزد</t>
+  </si>
+  <si>
+    <t>در حال ارسال</t>
+  </si>
+  <si>
+    <t>نسرین  انجذاب</t>
+  </si>
+  <si>
+    <t>یزد،ابن سینا، بل قندی, واحد ۲</t>
+  </si>
+  <si>
+    <t>09132513703</t>
+  </si>
+  <si>
+    <t>ژل و صابون ابرو</t>
+  </si>
+  <si>
+    <t>ژل لیفت ابرو کولمار مدل N | گارانتی اصالت و سلامت فیزیکی کالا</t>
+  </si>
+  <si>
+    <t>همدان-همدان</t>
+  </si>
+  <si>
+    <t>حمیدرضا حقیقی نیکو</t>
+  </si>
+  <si>
+    <t>همدان شهرک بهشتی نرسیده به میدان گلها روبرو مسجد ابتدای کوچه ارکیده مجتمع آفتاب واحد یک, پلاک ۵۷۱, واحد ۱</t>
+  </si>
+  <si>
+    <t>09918362967</t>
+  </si>
+  <si>
+    <t>مداد لب گلدن رز مدل Dream شماره 539 | گارانتی اصالت و سلامت فیزیکی کالا</t>
+  </si>
+  <si>
+    <t>خوزستان-اهواز</t>
+  </si>
+  <si>
+    <t>سارا بارونی بتوندی</t>
+  </si>
+  <si>
+    <t>کوی سلطانی منش خیابان ۱۷شهریور پلاک ۳۹</t>
+  </si>
+  <si>
+    <t>09160392873</t>
+  </si>
+  <si>
+    <t>مداد لب گلدن رز مدل Mood Defining شماره 09 | گارانتی اصالت و سلامت فیزیکی کالا</t>
+  </si>
+  <si>
+    <t>رژ لب جامد</t>
+  </si>
+  <si>
+    <t>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 215 | گارانتی اصالت و سلامت فیزیکی کالا</t>
+  </si>
+  <si>
+    <t>اسپری تثبیت کننده آرایش گلدن رز مدل Fixing حجم 120 میلی لیتر | گارانتی اصالت و سلامت فیزیکی کالا</t>
+  </si>
+  <si>
+    <t>مازندران-امیرکلا</t>
+  </si>
+  <si>
+    <t>فضیلت ضرابی</t>
+  </si>
+  <si>
+    <t>خ. علوی، نرسیده به خ. شجاعیان، خ. نیما چهار, پلاک ۵, واحد ۵</t>
+  </si>
+  <si>
+    <t>09112154402</t>
+  </si>
+  <si>
+    <t>ژل ابرو گلدن رز مدل Max Hold حجم 7 میلی لیتر | گارانتی اصالت و سلامت فیزیکی کالا</t>
+  </si>
+  <si>
+    <t>1405/06/31</t>
+  </si>
+  <si>
+    <t>آذربایجان غربی-ارومیه</t>
+  </si>
+  <si>
+    <t>دنیز فری</t>
+  </si>
+  <si>
+    <t>مدیریت، خ. کاشانی، خ. دفاع مقدس، خ. امداد، ک. 6, پلاک ۹</t>
+  </si>
+  <si>
+    <t>09306215594</t>
+  </si>
+  <si>
+    <t>سایه چشم</t>
+  </si>
+  <si>
+    <t>سایه چشم گلدن رز مدل Terracotta کد 120 | گارانتی اصالت و سلامت فیزیکی کالا</t>
+  </si>
+  <si>
+    <t>اصفهان-اصفهان</t>
+  </si>
+  <si>
+    <t>ایلیا زارع</t>
+  </si>
+  <si>
+    <t>آبشار سوم کوی شهید کشوری بلوار گلستان مجتمع دایموند طبقه۴ واحد ۳ه‍, پلاک ۱, واحد ۳۸</t>
+  </si>
+  <si>
+    <t>09134086081</t>
+  </si>
+  <si>
+    <t>سایه چشم گلدن رز مدل Terracotta کد 113 | گارانتی اصالت و سلامت فیزیکی کالا</t>
+  </si>
+  <si>
+    <t>رژ گونه</t>
+  </si>
+  <si>
+    <t>رژ گونه استیکی گلدن رز مدل Creamy شماره 102 | گارانتی اصالت و سلامت فیزیکی کالا</t>
+  </si>
+  <si>
+    <t>سمنان-گرمسار</t>
+  </si>
+  <si>
+    <t>فهیمه بهادر</t>
+  </si>
+  <si>
+    <t>شهرک قائم.انتهای خیابان صاحب الزمان .کوچه قشم.فهیمه بهادر, پلاک ۱</t>
+  </si>
+  <si>
+    <t>09128317861</t>
+  </si>
+  <si>
+    <t>رژ لب جامد گلدن رز شماره 16 | گارانتی اصالت و سلامت فیزیکی کالا</t>
+  </si>
+  <si>
+    <t>قم-قم</t>
+  </si>
+  <si>
+    <t>نرگس صفاری</t>
+  </si>
+  <si>
+    <t>بلوار الغدیر.کوچه ی 43, پلاک ۹, واحد باسلام</t>
+  </si>
+  <si>
+    <t>09120512232</t>
+  </si>
+  <si>
+    <t>اصفهان-آران و بیدگل</t>
+  </si>
+  <si>
+    <t>فرزانه انتظاریان</t>
+  </si>
+  <si>
+    <t>شهرک رسالت، بل مطهری، خ. حکمت ۱۱, پلاک ۱</t>
+  </si>
+  <si>
+    <t>09335650736</t>
   </si>
 </sst>
 </file>
@@ -540,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -640,23 +730,23 @@
         <v>25</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1">
-        <v>22344727</v>
+        <v>1761811</v>
       </c>
       <c r="E2" s="1">
-        <v>82230424</v>
+        <v>37203276</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1">
-        <v>376468553</v>
+        <v>376115701</v>
       </c>
       <c r="H2" s="1">
-        <v>384645345</v>
+        <v>384235175</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>28</v>
@@ -665,16 +755,16 @@
         <v>26</v>
       </c>
       <c r="K2" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" s="1">
-        <v>7704900</v>
+        <v>9411800</v>
       </c>
       <c r="M2" s="1">
         <v>1890000</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>27</v>
@@ -683,29 +773,29 @@
         <v>27</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="U2" s="1"/>
       <c r="V2" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
+      </c>
+      <c r="X2" s="1">
+        <v>8915887940</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -713,23 +803,23 @@
         <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D3" s="1">
-        <v>1051424</v>
+        <v>14926956</v>
       </c>
       <c r="E3" s="1">
-        <v>34359481</v>
+        <v>63117064</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1">
-        <v>376467280</v>
+        <v>376112991</v>
       </c>
       <c r="H3" s="1">
-        <v>384643778</v>
+        <v>384232053</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>28</v>
@@ -738,16 +828,16 @@
         <v>26</v>
       </c>
       <c r="K3" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3" s="1">
-        <v>3176000</v>
+        <v>4242100</v>
       </c>
       <c r="M3" s="1">
         <v>1890000</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>27</v>
@@ -756,29 +846,29 @@
         <v>27</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="R3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T3" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="U3" s="1"/>
       <c r="V3" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>27</v>
+        <v>46</v>
+      </c>
+      <c r="X3" s="1">
+        <v>6514883333</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -786,23 +876,23 @@
         <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D4" s="1">
-        <v>16417869</v>
+        <v>16651496</v>
       </c>
       <c r="E4" s="1">
-        <v>57178901</v>
+        <v>57918432</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1">
-        <v>376440662</v>
+        <v>376108343</v>
       </c>
       <c r="H4" s="1">
-        <v>384613025</v>
+        <v>384226719</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>28</v>
@@ -814,13 +904,13 @@
         <v>1</v>
       </c>
       <c r="L4" s="1">
-        <v>5990000</v>
+        <v>3074000</v>
       </c>
       <c r="M4" s="1">
         <v>1890000</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>27</v>
@@ -829,29 +919,29 @@
         <v>27</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>27</v>
+        <v>51</v>
+      </c>
+      <c r="X4" s="1">
+        <v>6174797981</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -859,23 +949,23 @@
         <v>25</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D5" s="1">
-        <v>10437360</v>
+        <v>21200215</v>
       </c>
       <c r="E5" s="1">
-        <v>38144310</v>
+        <v>76376317</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1">
-        <v>376319006</v>
+        <v>376108343</v>
       </c>
       <c r="H5" s="1">
-        <v>384473987</v>
+        <v>384226719</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>28</v>
@@ -887,13 +977,13 @@
         <v>1</v>
       </c>
       <c r="L5" s="1">
-        <v>5990000</v>
+        <v>3200000</v>
       </c>
       <c r="M5" s="1">
         <v>1890000</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>27</v>
@@ -902,29 +992,29 @@
         <v>27</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="X5" s="1">
-        <v>5615813343</v>
+        <v>6174797981</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -932,26 +1022,26 @@
         <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D6" s="1">
-        <v>6431103</v>
+        <v>22276872</v>
       </c>
       <c r="E6" s="1">
-        <v>34343986</v>
+        <v>81948608</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1">
-        <v>376314807</v>
+        <v>376108343</v>
       </c>
       <c r="H6" s="1">
-        <v>384469334</v>
+        <v>384226719</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>26</v>
@@ -960,13 +1050,13 @@
         <v>1</v>
       </c>
       <c r="L6" s="1">
-        <v>10499700</v>
+        <v>7046500</v>
       </c>
       <c r="M6" s="1">
         <v>1890000</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>27</v>
@@ -975,29 +1065,29 @@
         <v>27</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="W6" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="W6" s="1" t="s">
+      <c r="X6" s="1">
+        <v>6174797981</v>
+      </c>
+      <c r="Y6" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="X6" s="1">
-        <v>4681745784</v>
-      </c>
-      <c r="Y6" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1005,23 +1095,23 @@
         <v>25</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D7" s="1">
-        <v>10829220</v>
+        <v>1417903</v>
       </c>
       <c r="E7" s="1">
-        <v>49174543</v>
+        <v>17438302</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1">
-        <v>376300791</v>
+        <v>376050084</v>
       </c>
       <c r="H7" s="1">
-        <v>384453539</v>
+        <v>384156943</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>28</v>
@@ -1033,13 +1123,13 @@
         <v>1</v>
       </c>
       <c r="L7" s="1">
-        <v>4886600</v>
+        <v>7474200</v>
       </c>
       <c r="M7" s="1">
         <v>1890000</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>27</v>
@@ -1048,29 +1138,467 @@
         <v>27</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="U7" s="1"/>
       <c r="V7" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="X7" s="1">
-        <v>6481936891</v>
+        <v>4432768965</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="1">
+        <v>21199009</v>
+      </c>
+      <c r="E8" s="1">
+        <v>76377226</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1">
+        <v>376032844</v>
+      </c>
+      <c r="H8" s="1">
+        <v>384135079</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1">
+        <v>6229200</v>
+      </c>
+      <c r="M8" s="1">
+        <v>1890000</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="X8" s="1">
+        <v>5714715181</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="1">
+        <v>994911</v>
+      </c>
+      <c r="E9" s="1">
+        <v>41019819</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1">
+        <v>376018750</v>
+      </c>
+      <c r="H9" s="1">
+        <v>384118010</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1">
+        <v>9390000</v>
+      </c>
+      <c r="M9" s="1">
+        <v>1890000</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="X9" s="1">
+        <v>8169315977</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="1">
+        <v>8417479</v>
+      </c>
+      <c r="E10" s="1">
+        <v>41019789</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1">
+        <v>376018750</v>
+      </c>
+      <c r="H10" s="1">
+        <v>384118010</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1">
+        <v>9390000</v>
+      </c>
+      <c r="M10" s="1">
+        <v>1890000</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="X10" s="1">
+        <v>8169315977</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="1">
+        <v>515051</v>
+      </c>
+      <c r="E11" s="1">
+        <v>41021186</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1">
+        <v>375934146</v>
+      </c>
+      <c r="H11" s="1">
+        <v>384020366</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1">
+        <v>11990000</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1890000</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="X11" s="1">
+        <v>3581896961</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="1">
+        <v>7147064</v>
+      </c>
+      <c r="E12" s="1">
+        <v>31044531</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1">
+        <v>375923086</v>
+      </c>
+      <c r="H12" s="1">
+        <v>384007979</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="1">
+        <v>2</v>
+      </c>
+      <c r="L12" s="1">
+        <v>5381400</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1890000</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="X12" s="1">
+        <v>3716193390</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="1">
+        <v>6431103</v>
+      </c>
+      <c r="E13" s="1">
+        <v>34343986</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1">
+        <v>375921667</v>
+      </c>
+      <c r="H13" s="1">
+        <v>384006376</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>10499700</v>
+      </c>
+      <c r="M13" s="1">
+        <v>1890000</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="X13" s="1">
+        <v>6741649396</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
